--- a/data/trans_camb/P1408-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1408-Habitat-trans_camb.xlsx
@@ -634,29 +634,29 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>-0,28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,63</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>-0,14</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>-1,33</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,16</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,07</t>
+          <t>-2,28; 2,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -0,58</t>
+          <t>-3,77; -0,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,76</t>
+          <t>-2,15; 1,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,2</t>
+          <t>-1,77; 1,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,65</t>
+          <t>-2,01; 0,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,12</t>
+          <t>-0,64; 1,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,29</t>
+          <t>-1,42; 1,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -0,32</t>
+          <t>-2,43; -0,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,38</t>
+          <t>-0,98; 1,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-4,02%</t>
+          <t>-8,14%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 88,3</t>
+          <t>-52,97; 87,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-81,03; -17,91</t>
+          <t>-81,25; -8,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 68,86</t>
+          <t>-46,19; 67,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,78; 84,51</t>
+          <t>-62,94; 100,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,6; 50,49</t>
+          <t>-72,73; 65,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 168,7</t>
+          <t>-24,84; 143,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,57; 62,91</t>
+          <t>-42,68; 53,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,78; -10,45</t>
+          <t>-71,0; -13,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 62,61</t>
+          <t>-28,53; 62,43</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,26</t>
+          <t>-2,86</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-1,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -1,59</t>
+          <t>-4,95; -1,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -1,36</t>
+          <t>-4,68; -1,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; -1,7</t>
+          <t>-4,6; -1,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; -0,41</t>
+          <t>-3,04; -0,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,04</t>
+          <t>-2,72; -0,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,55</t>
+          <t>-1,56; 1,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; -1,51</t>
+          <t>-3,6; -1,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -1,09</t>
+          <t>-3,36; -1,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; -0,67</t>
+          <t>-2,5; -0,26</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-63,0%</t>
+          <t>-55,32%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,39%</t>
+          <t>-2,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-43,22%</t>
+          <t>-37,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,54; -35,77</t>
+          <t>-77,71; -35,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-76,38; -29,98</t>
+          <t>-75,55; -31,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,71; -38,82</t>
+          <t>-71,63; -27,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,93; -19,37</t>
+          <t>-84,19; -23,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,35; 8,03</t>
+          <t>-75,91; 5,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,81; 98,68</t>
+          <t>-45,22; 73,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,24; -44,68</t>
+          <t>-76,75; -38,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,58; -31,24</t>
+          <t>-71,16; -33,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,74; -20,68</t>
+          <t>-55,44; -7,83</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,16</t>
+          <t>-1,29</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-1,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,12</t>
+          <t>-3,56; 0,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -0,36</t>
+          <t>-3,75; -0,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,49</t>
+          <t>-3,18; 0,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -0,74</t>
+          <t>-3,71; -0,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,15</t>
+          <t>-3,09; 0,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,07</t>
+          <t>-2,86; 0,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,89</t>
+          <t>-3,1; -0,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,51</t>
+          <t>-2,88; -0,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; -0,3</t>
+          <t>-2,56; -0,16</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-32,89%</t>
+          <t>-36,54%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-51,51%</t>
+          <t>-38,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-43,41%</t>
+          <t>-37,63%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-74,3; 13,06</t>
+          <t>-75,04; 11,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,46; -3,67</t>
+          <t>-81,17; -3,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-63,45; 22,0</t>
+          <t>-66,1; 22,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-89,6; -26,61</t>
+          <t>-88,41; -26,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,36; 9,45</t>
+          <t>-74,67; 13,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,04; -5,79</t>
+          <t>-69,41; 16,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,83; -29,41</t>
+          <t>-76,08; -28,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,1; -16,47</t>
+          <t>-69,73; -15,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,19; -12,06</t>
+          <t>-60,55; -4,8</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,57</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; -1,22</t>
+          <t>-3,87; -1,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; -0,12</t>
+          <t>-3,26; -0,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,16</t>
+          <t>-2,99; -0,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; -0,54</t>
+          <t>-2,96; -0,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,41; -1,15</t>
+          <t>-3,51; -1,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,22</t>
+          <t>-1,37; 1,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -1,13</t>
+          <t>-3,05; -1,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,98</t>
+          <t>-3,01; -1,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,21</t>
+          <t>-1,66; 0,24</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-38,63%</t>
+          <t>-35,73%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-23,16%</t>
+          <t>-19,15%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-79,71; -33,56</t>
+          <t>-78,5; -28,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-63,92; -2,46</t>
+          <t>-65,77; -7,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,86; -3,46</t>
+          <t>-60,55; 1,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-78,55; -24,03</t>
+          <t>-76,19; -11,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-90,02; -42,42</t>
+          <t>-90,33; -44,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 56,19</t>
+          <t>-36,21; 61,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-74,18; -37,98</t>
+          <t>-74,28; -37,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-71,81; -33,36</t>
+          <t>-71,7; -33,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,94; 7,09</t>
+          <t>-39,92; 10,43</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,0</t>
+          <t>-0,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; -1,05</t>
+          <t>-2,95; -1,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -1,33</t>
+          <t>-3,07; -1,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; -0,84</t>
+          <t>-2,38; -0,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; -0,86</t>
+          <t>-2,12; -0,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; -0,8</t>
+          <t>-2,18; -0,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,47</t>
+          <t>-0,91; 0,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -1,19</t>
+          <t>-2,37; -1,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -1,29</t>
+          <t>-2,36; -1,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,33</t>
+          <t>-1,41; -0,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-41,68%</t>
+          <t>-38,58%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-10,53%</t>
+          <t>-5,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-29,15%</t>
+          <t>-25,12%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,18; -28,96</t>
+          <t>-63,61; -30,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-65,19; -36,12</t>
+          <t>-65,26; -38,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,71; -23,44</t>
+          <t>-51,62; -21,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-70,45; -35,17</t>
+          <t>-68,85; -35,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-68,41; -32,66</t>
+          <t>-68,29; -32,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 20,86</t>
+          <t>-29,05; 23,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-61,51; -38,14</t>
+          <t>-62,78; -39,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-62,47; -40,49</t>
+          <t>-63,3; -41,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,91; -10,66</t>
+          <t>-38,19; -10,22</t>
         </is>
       </c>
     </row>
